--- a/ET-release8.1/Unity/Assets/Config/Excel/ExternalDisplayConfig.xlsx
+++ b/ET-release8.1/Unity/Assets/Config/Excel/ExternalDisplayConfig.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="140">
   <si>
     <t>#</t>
   </si>
@@ -428,6 +428,30 @@
   </si>
   <si>
     <t>女裤子2</t>
+  </si>
+  <si>
+    <t>rabbitboddy1</t>
+  </si>
+  <si>
+    <t>兔子1</t>
+  </si>
+  <si>
+    <t>rabbitboddy2</t>
+  </si>
+  <si>
+    <t>兔子2</t>
+  </si>
+  <si>
+    <t>rabbitmanbody1</t>
+  </si>
+  <si>
+    <t>兔子男1</t>
+  </si>
+  <si>
+    <t>rabbitmanbody2</t>
+  </si>
+  <si>
+    <t>兔子男2</t>
   </si>
 </sst>
 </file>
@@ -1418,7 +1442,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C2:K61"/>
+  <dimension ref="C2:K65"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -3148,6 +3172,122 @@
         <v>131</v>
       </c>
     </row>
+    <row r="62" s="1" customFormat="1" spans="3:11">
+      <c r="C62" s="1">
+        <v>1057</v>
+      </c>
+      <c r="D62" s="1">
+        <v>10500000</v>
+      </c>
+      <c r="E62" s="1">
+        <v>0</v>
+      </c>
+      <c r="F62" s="1">
+        <v>5</v>
+      </c>
+      <c r="G62" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="H62" s="1">
+        <v>1</v>
+      </c>
+      <c r="I62" s="1">
+        <v>0</v>
+      </c>
+      <c r="J62" s="1">
+        <v>0</v>
+      </c>
+      <c r="K62" s="4" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="63" s="1" customFormat="1" spans="3:11">
+      <c r="C63" s="1">
+        <v>1058</v>
+      </c>
+      <c r="D63" s="1">
+        <v>10500001</v>
+      </c>
+      <c r="E63" s="1">
+        <v>0</v>
+      </c>
+      <c r="F63" s="1">
+        <v>5</v>
+      </c>
+      <c r="G63" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="H63" s="1">
+        <v>1</v>
+      </c>
+      <c r="I63" s="1">
+        <v>1</v>
+      </c>
+      <c r="J63" s="1">
+        <v>0</v>
+      </c>
+      <c r="K63" s="4" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="64" s="1" customFormat="1" spans="3:11">
+      <c r="C64" s="1">
+        <v>1059</v>
+      </c>
+      <c r="D64" s="1">
+        <v>10501000</v>
+      </c>
+      <c r="E64" s="1">
+        <v>1</v>
+      </c>
+      <c r="F64" s="1">
+        <v>5</v>
+      </c>
+      <c r="G64" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="H64" s="1">
+        <v>1</v>
+      </c>
+      <c r="I64" s="1">
+        <v>0</v>
+      </c>
+      <c r="J64" s="1">
+        <v>0</v>
+      </c>
+      <c r="K64" s="4" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="65" s="1" customFormat="1" spans="3:11">
+      <c r="C65" s="1">
+        <v>1060</v>
+      </c>
+      <c r="D65" s="1">
+        <v>10501001</v>
+      </c>
+      <c r="E65" s="1">
+        <v>1</v>
+      </c>
+      <c r="F65" s="1">
+        <v>5</v>
+      </c>
+      <c r="G65" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="H65" s="1">
+        <v>1</v>
+      </c>
+      <c r="I65" s="1">
+        <v>1</v>
+      </c>
+      <c r="J65" s="1">
+        <v>0</v>
+      </c>
+      <c r="K65" s="4" t="s">
+        <v>139</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/ET-release8.1/Unity/Assets/Config/Excel/ExternalDisplayConfig.xlsx
+++ b/ET-release8.1/Unity/Assets/Config/Excel/ExternalDisplayConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="20340" windowHeight="11775"/>
+    <workbookView windowWidth="22500" windowHeight="13275"/>
   </bookViews>
   <sheets>
     <sheet name="ExternalDisplayProto" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="326">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="325">
   <si>
     <t>Id</t>
   </si>
@@ -835,7 +835,7 @@
     <t>Shield_1</t>
   </si>
   <si>
-    <t>武器·左手·盾1211</t>
+    <t>武器·右手·盾1211</t>
   </si>
   <si>
     <t>Soon_Spear</t>
@@ -1007,9 +1007,6 @@
   </si>
   <si>
     <t>马·配饰1255</t>
-  </si>
-  <si>
-    <t>武器·右手·盾1211</t>
   </si>
 </sst>
 </file>
@@ -1997,7 +1994,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C2:F260"/>
+  <dimension ref="C3:F260"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -5001,7 +4998,7 @@
         <v>266</v>
       </c>
       <c r="F216" s="1" t="s">
-        <v>325</v>
+        <v>267</v>
       </c>
     </row>
     <row r="217" s="1" customFormat="1" spans="3:6">
